--- a/erp-server/erp-server-wms/src/main/resources/excel/pdaMoveInfoTemplate.xlsx
+++ b/erp-server/erp-server-wms/src/main/resources/excel/pdaMoveInfoTemplate.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="22890" windowHeight="11265"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -678,7 +678,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -687,9 +687,18 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1219,34 +1228,40 @@
   <dimension ref="A1:F2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="2" width="16.875" customWidth="1"/>
-    <col min="3" max="3" width="25.5" customWidth="1"/>
-    <col min="4" max="4" width="26.25" customWidth="1"/>
+    <col min="1" max="2" width="16.875" style="3" customWidth="1"/>
+    <col min="3" max="3" width="25.5" style="3" customWidth="1"/>
+    <col min="4" max="4" width="26.25" style="3" customWidth="1"/>
     <col min="5" max="5" width="20" customWidth="1"/>
-    <col min="6" max="6" width="16.875" customWidth="1"/>
+    <col min="6" max="6" width="16.875" style="3" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" ht="15" spans="1:6">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="4" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2" s="2" customFormat="1"/>
+    <row r="2" s="2" customFormat="1" spans="1:6">
+      <c r="A2" s="6"/>
+      <c r="B2" s="6"/>
+      <c r="C2" s="6"/>
+      <c r="D2" s="6"/>
+      <c r="F2" s="6"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>

--- a/erp-server/erp-server-wms/src/main/resources/excel/pdaMoveInfoTemplate.xlsx
+++ b/erp-server/erp-server-wms/src/main/resources/excel/pdaMoveInfoTemplate.xlsx
@@ -29,19 +29,99 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
   <si>
-    <t>SKU</t>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>SKU</t>
+    </r>
   </si>
   <si>
-    <t>仓库</t>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>仓库</t>
+    </r>
   </si>
   <si>
-    <t>取货仓位</t>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>取货仓位</t>
+    </r>
   </si>
   <si>
-    <t>上架仓位</t>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>上架仓位</t>
+    </r>
   </si>
   <si>
-    <t>移动数量</t>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>移动数量</t>
+    </r>
   </si>
   <si>
     <t>备注</t>
@@ -57,7 +137,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -71,6 +151,12 @@
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="13"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="13"/>
@@ -548,137 +634,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -695,6 +781,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
@@ -1251,16 +1340,16 @@
       <c r="E1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="F1" s="6" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="2" s="2" customFormat="1" spans="1:6">
-      <c r="A2" s="6"/>
-      <c r="B2" s="6"/>
-      <c r="C2" s="6"/>
-      <c r="D2" s="6"/>
-      <c r="F2" s="6"/>
+      <c r="A2" s="7"/>
+      <c r="B2" s="7"/>
+      <c r="C2" s="7"/>
+      <c r="D2" s="7"/>
+      <c r="F2" s="7"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
